--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cposb\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05726E89-3FD8-4C1B-8709-90C2F289768E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD11466-8A17-441F-AC81-380BF66B2C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3255" yWindow="1380" windowWidth="22305" windowHeight="13425" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="How to update" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="974">
   <si>
     <t>Lot #</t>
   </si>
@@ -2925,6 +2925,27 @@
   </si>
   <si>
     <t>610070-2025-25018S</t>
+  </si>
+  <si>
+    <t>Photo</t>
+  </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t>Lot_47.jpg</t>
+  </si>
+  <si>
+    <t>Lot_48.jpg</t>
+  </si>
+  <si>
+    <t>Lot_145.jpg</t>
+  </si>
+  <si>
+    <t>Lot_146.jpg</t>
   </si>
 </sst>
 </file>
@@ -4065,7 +4086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AG43"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="7.375" style="56" customWidth="1"/>
@@ -4098,7 +4119,7 @@
     <col min="31" max="16384" width="10" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="50" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:33" s="50" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
@@ -4181,8 +4202,17 @@
       <c r="AD1" s="145" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+      <c r="AE1" s="50" t="s">
+        <v>967</v>
+      </c>
+      <c r="AF1" s="50" t="s">
+        <v>968</v>
+      </c>
+      <c r="AG1" s="50" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>26</v>
       </c>
@@ -4243,7 +4273,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="3" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>33</v>
       </c>
@@ -4297,7 +4327,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="4" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>34</v>
       </c>
@@ -4357,7 +4387,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="5" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>40</v>
       </c>
@@ -4417,7 +4447,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="6" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>44</v>
       </c>
@@ -4476,7 +4506,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="7" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>50</v>
       </c>
@@ -4535,7 +4565,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="8" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>54</v>
       </c>
@@ -4586,7 +4616,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="9" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>56</v>
       </c>
@@ -4637,7 +4667,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="10" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>57</v>
       </c>
@@ -4697,7 +4727,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="11" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>61</v>
       </c>
@@ -4757,7 +4787,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="12" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>65</v>
       </c>
@@ -4816,7 +4846,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="13" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>69</v>
       </c>
@@ -4881,7 +4911,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="14" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>73</v>
       </c>
@@ -4923,7 +4953,7 @@
       </c>
       <c r="Y14" s="80"/>
     </row>
-    <row r="15" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="15" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>76</v>
       </c>
@@ -4965,7 +4995,7 @@
       <c r="X15" s="29"/>
       <c r="Y15" s="80"/>
     </row>
-    <row r="16" spans="1:30" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="16" spans="1:33" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>79</v>
       </c>
@@ -6487,7 +6517,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AH16"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
@@ -6512,7 +6542,7 @@
     <col min="31" max="31" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="1" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:34" s="1" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6597,8 +6627,17 @@
       <c r="AE1" s="146" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" ht="18" customHeight="1">
+      <c r="AF1" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" ht="18" customHeight="1">
       <c r="A2" s="19" t="s">
         <v>179</v>
       </c>
@@ -6647,7 +6686,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="18" customHeight="1">
+    <row r="3" spans="1:34" ht="18" customHeight="1">
       <c r="A3" s="19" t="s">
         <v>183</v>
       </c>
@@ -6696,7 +6735,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="18" customHeight="1">
+    <row r="4" spans="1:34" ht="18" customHeight="1">
       <c r="A4" s="19" t="s">
         <v>185</v>
       </c>
@@ -6742,7 +6781,7 @@
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
     </row>
-    <row r="5" spans="1:31" ht="18" customHeight="1">
+    <row r="5" spans="1:34" ht="18" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>187</v>
       </c>
@@ -6788,7 +6827,7 @@
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
     </row>
-    <row r="6" spans="1:31" s="36" customFormat="1" ht="18" customHeight="1">
+    <row r="6" spans="1:34" s="36" customFormat="1" ht="18" customHeight="1">
       <c r="A6" s="37"/>
       <c r="D6" s="37"/>
       <c r="E6" s="38"/>
@@ -6807,7 +6846,7 @@
       <c r="X6" s="40"/>
       <c r="Y6" s="40"/>
     </row>
-    <row r="7" spans="1:31" ht="18" customHeight="1">
+    <row r="7" spans="1:34" ht="18" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>189</v>
       </c>
@@ -6858,8 +6897,11 @@
       <c r="Z7" s="84"/>
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
-    </row>
-    <row r="8" spans="1:31" ht="18" customHeight="1">
+      <c r="AF7" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" ht="18" customHeight="1">
       <c r="A8" s="19" t="s">
         <v>192</v>
       </c>
@@ -6910,8 +6952,11 @@
       <c r="Z8" s="84"/>
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
-    </row>
-    <row r="9" spans="1:31" ht="18" customHeight="1">
+      <c r="AF8" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" ht="18" customHeight="1">
       <c r="A9" s="19" t="s">
         <v>195</v>
       </c>
@@ -6963,7 +7008,7 @@
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
     </row>
-    <row r="10" spans="1:31" s="47" customFormat="1" ht="18" customHeight="1">
+    <row r="10" spans="1:34" s="47" customFormat="1" ht="18" customHeight="1">
       <c r="A10" s="41"/>
       <c r="B10" s="42"/>
       <c r="C10" s="42"/>
@@ -6993,7 +7038,7 @@
       <c r="AA10" s="42"/>
       <c r="AB10" s="42"/>
     </row>
-    <row r="11" spans="1:31" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="11" spans="1:34" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A11" s="85" t="s">
         <v>197</v>
       </c>
@@ -7039,7 +7084,7 @@
       <c r="AA11" s="86"/>
       <c r="AB11" s="86"/>
     </row>
-    <row r="12" spans="1:31" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="12" spans="1:34" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A12" s="85" t="s">
         <v>202</v>
       </c>
@@ -7085,7 +7130,7 @@
       <c r="AA12" s="86"/>
       <c r="AB12" s="86"/>
     </row>
-    <row r="13" spans="1:31" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="13" spans="1:34" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A13" s="85" t="s">
         <v>205</v>
       </c>
@@ -7136,7 +7181,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="14" spans="1:34" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A14" s="85" t="s">
         <v>208</v>
       </c>
@@ -7182,7 +7227,7 @@
       <c r="AA14" s="86"/>
       <c r="AB14" s="86"/>
     </row>
-    <row r="15" spans="1:31" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="15" spans="1:34" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A15" s="85" t="s">
         <v>211</v>
       </c>
@@ -7226,7 +7271,7 @@
       <c r="AA15" s="86"/>
       <c r="AB15" s="86"/>
     </row>
-    <row r="16" spans="1:31" s="47" customFormat="1"/>
+    <row r="16" spans="1:34" s="47" customFormat="1"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 I6" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -7248,7 +7293,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AE93"/>
+  <dimension ref="A1:AH93"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="8.625" style="28" customWidth="1"/>
@@ -7277,7 +7322,7 @@
     <col min="32" max="16384" width="10.875" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="50" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:34" s="50" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -7362,8 +7407,17 @@
       <c r="AE1" s="145" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" s="4" customFormat="1" ht="18.95" customHeight="1">
+      <c r="AF1" s="50" t="s">
+        <v>967</v>
+      </c>
+      <c r="AG1" s="50" t="s">
+        <v>968</v>
+      </c>
+      <c r="AH1" s="50" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" s="4" customFormat="1" ht="18.95" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>214</v>
       </c>
@@ -7429,7 +7483,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:31" s="4" customFormat="1" ht="18.95" customHeight="1">
+    <row r="3" spans="1:34" s="4" customFormat="1" ht="18.95" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>220</v>
       </c>
@@ -7495,7 +7549,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="4" spans="1:31" s="4" customFormat="1" ht="18.95" customHeight="1">
+    <row r="4" spans="1:34" s="4" customFormat="1" ht="18.95" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>225</v>
       </c>
@@ -7561,7 +7615,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="4" customFormat="1" ht="18.95" customHeight="1">
+    <row r="5" spans="1:34" s="4" customFormat="1" ht="18.95" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>229</v>
       </c>
@@ -7627,7 +7681,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="6" spans="1:31" s="4" customFormat="1" ht="18.95" customHeight="1">
+    <row r="6" spans="1:34" s="4" customFormat="1" ht="18.95" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>233</v>
       </c>
@@ -7693,7 +7747,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="7" spans="1:31" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="7" spans="1:34" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A7" s="72">
         <v>55</v>
       </c>
@@ -7764,7 +7818,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="8" spans="1:34" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A8" s="72" t="s">
         <v>242</v>
       </c>
@@ -7833,7 +7887,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="9" spans="1:34" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A9" s="72" t="s">
         <v>247</v>
       </c>
@@ -7905,7 +7959,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="10" spans="1:34" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A10" s="72" t="s">
         <v>252</v>
       </c>
@@ -7974,7 +8028,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="11" spans="1:34" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A11" s="72" t="s">
         <v>257</v>
       </c>
@@ -8043,7 +8097,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="12" spans="1:31" s="4" customFormat="1" ht="18.95" customHeight="1">
+    <row r="12" spans="1:34" s="4" customFormat="1" ht="18.95" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>262</v>
       </c>
@@ -8106,7 +8160,7 @@
       <c r="Y12" s="70"/>
       <c r="Z12" s="71"/>
     </row>
-    <row r="13" spans="1:31" s="4" customFormat="1" ht="18.95" customHeight="1">
+    <row r="13" spans="1:34" s="4" customFormat="1" ht="18.95" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>266</v>
       </c>
@@ -8169,7 +8223,7 @@
       <c r="Y13" s="70"/>
       <c r="Z13" s="71"/>
     </row>
-    <row r="14" spans="1:31" s="4" customFormat="1" ht="18.95" customHeight="1">
+    <row r="14" spans="1:34" s="4" customFormat="1" ht="18.95" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>270</v>
       </c>
@@ -8232,7 +8286,7 @@
       <c r="Y14" s="70"/>
       <c r="Z14" s="71"/>
     </row>
-    <row r="15" spans="1:31" s="4" customFormat="1" ht="18.95" customHeight="1">
+    <row r="15" spans="1:34" s="4" customFormat="1" ht="18.95" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>274</v>
       </c>
@@ -8295,7 +8349,7 @@
       <c r="Y15" s="70"/>
       <c r="Z15" s="71"/>
     </row>
-    <row r="16" spans="1:31" s="4" customFormat="1" ht="18.95" customHeight="1">
+    <row r="16" spans="1:34" s="4" customFormat="1" ht="18.95" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>278</v>
       </c>
@@ -11824,7 +11878,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AE194"/>
+  <dimension ref="A1:AH194"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="8.375" style="64" customWidth="1"/>
@@ -11853,7 +11907,7 @@
     <col min="32" max="16384" width="10" style="64"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="50" customFormat="1" ht="18" customHeight="1">
+    <row r="1" spans="1:34" s="50" customFormat="1" ht="18" customHeight="1">
       <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
@@ -11939,8 +11993,17 @@
       <c r="AE1" s="145" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+      <c r="AF1" s="50" t="s">
+        <v>967</v>
+      </c>
+      <c r="AG1" s="50" t="s">
+        <v>968</v>
+      </c>
+      <c r="AH1" s="50" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>452</v>
       </c>
@@ -12005,7 +12068,7 @@
       <c r="Z2" s="117"/>
       <c r="AB2" s="127"/>
     </row>
-    <row r="3" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="3" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>455</v>
       </c>
@@ -12070,7 +12133,7 @@
       <c r="Z3" s="117"/>
       <c r="AB3" s="127"/>
     </row>
-    <row r="4" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="4" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>456</v>
       </c>
@@ -12135,7 +12198,7 @@
       <c r="Z4" s="117"/>
       <c r="AB4" s="127"/>
     </row>
-    <row r="5" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="5" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>457</v>
       </c>
@@ -12200,7 +12263,7 @@
       <c r="Z5" s="117"/>
       <c r="AB5" s="127"/>
     </row>
-    <row r="6" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="6" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>458</v>
       </c>
@@ -12265,7 +12328,7 @@
       <c r="Z6" s="117"/>
       <c r="AB6" s="127"/>
     </row>
-    <row r="7" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="7" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>459</v>
       </c>
@@ -12336,7 +12399,7 @@
       <c r="Z7" s="118"/>
       <c r="AB7" s="127"/>
     </row>
-    <row r="8" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="8" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>462</v>
       </c>
@@ -12407,7 +12470,7 @@
       <c r="Z8" s="118"/>
       <c r="AB8" s="127"/>
     </row>
-    <row r="9" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="9" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A9" s="5" t="s">
         <v>464</v>
       </c>
@@ -12478,7 +12541,7 @@
       <c r="Z9" s="118"/>
       <c r="AB9" s="127"/>
     </row>
-    <row r="10" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="10" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>466</v>
       </c>
@@ -12549,7 +12612,7 @@
       <c r="Z10" s="118"/>
       <c r="AB10" s="127"/>
     </row>
-    <row r="11" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="11" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A11" s="5" t="s">
         <v>468</v>
       </c>
@@ -12620,7 +12683,7 @@
       <c r="Z11" s="118"/>
       <c r="AB11" s="127"/>
     </row>
-    <row r="12" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="12" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A12" s="4">
         <v>91</v>
       </c>
@@ -12691,7 +12754,7 @@
       <c r="Z12" s="118"/>
       <c r="AB12" s="127"/>
     </row>
-    <row r="13" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="13" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>473</v>
       </c>
@@ -12762,7 +12825,7 @@
       <c r="Z13" s="118"/>
       <c r="AB13" s="127"/>
     </row>
-    <row r="14" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="14" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A14" s="5" t="s">
         <v>475</v>
       </c>
@@ -12833,7 +12896,7 @@
       <c r="Z14" s="118"/>
       <c r="AB14" s="127"/>
     </row>
-    <row r="15" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="15" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A15" s="5" t="s">
         <v>477</v>
       </c>
@@ -12904,7 +12967,7 @@
       <c r="Z15" s="118"/>
       <c r="AB15" s="127"/>
     </row>
-    <row r="16" spans="1:31" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="16" spans="1:34" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A16" s="5" t="s">
         <v>479</v>
       </c>
@@ -18455,7 +18518,7 @@
       <c r="AA96" s="60"/>
       <c r="AB96" s="127"/>
     </row>
-    <row r="97" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="97" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A97" s="5" t="s">
         <v>716</v>
       </c>
@@ -18526,7 +18589,7 @@
       <c r="Z97" s="118"/>
       <c r="AB97" s="127"/>
     </row>
-    <row r="98" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="98" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A98" s="5" t="s">
         <v>718</v>
       </c>
@@ -18597,7 +18660,7 @@
       <c r="Z98" s="118"/>
       <c r="AB98" s="127"/>
     </row>
-    <row r="99" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="99" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A99" s="5" t="s">
         <v>720</v>
       </c>
@@ -18668,7 +18731,7 @@
       <c r="Z99" s="118"/>
       <c r="AB99" s="127"/>
     </row>
-    <row r="100" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="100" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A100" s="5" t="s">
         <v>722</v>
       </c>
@@ -18739,7 +18802,7 @@
       <c r="Z100" s="118"/>
       <c r="AB100" s="127"/>
     </row>
-    <row r="101" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="101" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A101" s="5" t="s">
         <v>724</v>
       </c>
@@ -18810,7 +18873,7 @@
       <c r="Z101" s="118"/>
       <c r="AB101" s="127"/>
     </row>
-    <row r="102" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="102" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A102" s="4">
         <v>145</v>
       </c>
@@ -18876,8 +18939,11 @@
       <c r="Y102" s="59"/>
       <c r="Z102" s="118"/>
       <c r="AB102" s="127"/>
-    </row>
-    <row r="103" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+      <c r="AF102" s="4" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="103" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A103" s="5" t="s">
         <v>728</v>
       </c>
@@ -18943,8 +19009,11 @@
       <c r="Y103" s="59"/>
       <c r="Z103" s="118"/>
       <c r="AB103" s="127"/>
-    </row>
-    <row r="104" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+      <c r="AF103" s="4" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="104" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A104" s="5" t="s">
         <v>730</v>
       </c>
@@ -19010,8 +19079,11 @@
       <c r="Y104" s="59"/>
       <c r="Z104" s="118"/>
       <c r="AB104" s="127"/>
-    </row>
-    <row r="105" spans="1:28" s="89" customFormat="1" ht="18" customHeight="1">
+      <c r="AF104" s="4" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="105" spans="1:32" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A105" s="85" t="s">
         <v>733</v>
       </c>
@@ -19077,7 +19149,7 @@
       <c r="AA105" s="4"/>
       <c r="AB105" s="128"/>
     </row>
-    <row r="106" spans="1:28" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="106" spans="1:32" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A106" s="85" t="s">
         <v>738</v>
       </c>
@@ -19145,7 +19217,7 @@
       </c>
       <c r="AB106" s="128"/>
     </row>
-    <row r="107" spans="1:28" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="107" spans="1:32" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A107" s="85" t="s">
         <v>743</v>
       </c>
@@ -19213,7 +19285,7 @@
       </c>
       <c r="AB107" s="128"/>
     </row>
-    <row r="108" spans="1:28" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="108" spans="1:32" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A108" s="85" t="s">
         <v>748</v>
       </c>
@@ -19279,7 +19351,7 @@
       </c>
       <c r="AB108" s="128"/>
     </row>
-    <row r="109" spans="1:28" s="89" customFormat="1" ht="18" customHeight="1">
+    <row r="109" spans="1:32" s="89" customFormat="1" ht="18" customHeight="1">
       <c r="A109" s="85" t="s">
         <v>753</v>
       </c>
@@ -19347,7 +19419,7 @@
       </c>
       <c r="AB109" s="128"/>
     </row>
-    <row r="110" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="110" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A110" s="5" t="s">
         <v>758</v>
       </c>
@@ -19411,7 +19483,7 @@
       <c r="Z110" s="118"/>
       <c r="AB110" s="127"/>
     </row>
-    <row r="111" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="111" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A111" s="5" t="s">
         <v>759</v>
       </c>
@@ -19475,7 +19547,7 @@
       <c r="Z111" s="118"/>
       <c r="AB111" s="127"/>
     </row>
-    <row r="112" spans="1:28" s="4" customFormat="1" ht="18" customHeight="1">
+    <row r="112" spans="1:32" s="4" customFormat="1" ht="18" customHeight="1">
       <c r="A112" s="5" t="s">
         <v>760</v>
       </c>
